--- a/output/pdf_financials_xlsx/SGD.xlsx
+++ b/output/pdf_financials_xlsx/SGD.xlsx
@@ -4284,16 +4284,16 @@
         <v>-0.26335</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>-0.408079</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>0.070691</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.502037</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-0.597221</v>
       </c>
     </row>
     <row r="104">
@@ -4404,16 +4404,16 @@
         <v>0.580002</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>-0.170766</v>
+        <v>-0.5788450000000001</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.388392</v>
+        <v>0.459083</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>-0.660748</v>
+        <v>-1.162785</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.178651</v>
+        <v>-0.41857</v>
       </c>
     </row>
     <row r="107">
@@ -7213,7 +7213,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -10676,7 +10680,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SGD.xlsx
+++ b/output/pdf_financials_xlsx/SGD.xlsx
@@ -847,15 +847,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v>0.001898</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>5e-06</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1741,13 +1737,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.146777</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.222258</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.027213</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>3.917754</v>
@@ -1813,13 +1809,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.146777</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.222258</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.027213</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>3.917754</v>
@@ -2245,13 +2241,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.186818</v>
+        <v>0.040041</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.292696</v>
+        <v>0.070438</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.08167199999999999</v>
+        <v>0.054459</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.26335</v>
@@ -5126,16 +5122,16 @@
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.100231</v>
       </c>
     </row>
     <row r="125">
@@ -5166,16 +5162,16 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.100231</v>
       </c>
     </row>
     <row r="126">
@@ -9118,7 +9114,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -11026,7 +11022,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -23078,7 +23078,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">

--- a/output/pdf_financials_xlsx/SGD.xlsx
+++ b/output/pdf_financials_xlsx/SGD.xlsx
@@ -4646,7 +4646,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
@@ -11205,7 +11205,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SGD.xlsx
+++ b/output/pdf_financials_xlsx/SGD.xlsx
@@ -4437,19 +4437,19 @@
         <v>0</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.312753</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>8.222246</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>21.148349</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>28.072954</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>8.642073</v>
       </c>
     </row>
     <row r="108">
@@ -4557,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.05297</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -10102,7 +10102,11 @@
           <t>Share-based payment expense</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -12314,7 +12318,11 @@
           <t>Share-based payment expense - - - 8,074,571</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -12855,7 +12863,11 @@
           <t>Share-based payment expense - - - 9,909,216</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -13392,7 +13404,11 @@
           <t>Share-based payment expense - - - 9,909,216</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -13984,7 +14000,11 @@
           <t>Share-based payment expense - - - 5,616,048</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -14830,7 +14850,11 @@
           <t>Share-based payment expense - - 5,616,048</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -15440,7 +15464,11 @@
           <t>Share based payment expense - - 1,303,099</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -15743,7 +15771,11 @@
           <t>Share based payment expense 1,303,099</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -16416,7 +16448,11 @@
           <t>Proceeds from private placement 25,227,866</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -17087,7 +17123,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -17148,7 +17188,11 @@
           <t>Share based payment expense</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -17512,7 +17556,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
